--- a/data/trans_dic/P21D_6_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,9</t>
+          <t>0,51; 2,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,61</t>
+          <t>0,27; 1,63</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,03</t>
+          <t>0,16; 1,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,16; 1,39</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,91</t>
+          <t>1,53; 5,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,1</t>
+          <t>1,11; 3,44</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,04</t>
+          <t>1,0; 4,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,55</t>
+          <t>0,74; 2,72</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,75</t>
+          <t>0,33; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,2; 2,16</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,08</t>
+          <t>0,22; 1,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,82</t>
+          <t>0,85; 1,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,24</t>
+          <t>0,59; 1,22</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3690</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8945</t>
+          <t>0; 9697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8900</t>
+          <t>0; 9872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11535</t>
+          <t>0; 11547</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1337; 7484</t>
+          <t>1325; 7585</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1329; 7639</t>
+          <t>1301; 7698</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9215</t>
+          <t>0; 9591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>677; 6504</t>
+          <t>527; 6139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1482; 12854</t>
+          <t>1378; 11779</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8591</t>
+          <t>0; 7581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3268; 11162</t>
+          <t>3489; 11507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4710; 14422</t>
+          <t>5167; 15972</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4372</t>
+          <t>0; 3576</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1722; 7483</t>
+          <t>1860; 7724</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2162; 8677</t>
+          <t>2536; 9280</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>559; 4670</t>
+          <t>562; 5154</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>589; 5692</t>
+          <t>576; 6230</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3352; 17969</t>
+          <t>3735; 17563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13392; 29039</t>
+          <t>13469; 29134</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19536; 40407</t>
+          <t>19316; 39603</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_6_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Edad-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,94</t>
+          <t>0,46; 2,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,63</t>
+          <t>0,26; 1,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,29; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,91</t>
+          <t>0,19; 1,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,34; 1,7</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,06</t>
+          <t>1,29; 4,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,44</t>
+          <t>0,98; 3,03</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,17</t>
+          <t>1,12; 4,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,72</t>
+          <t>0,69; 2,69</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,03</t>
+          <t>0,3; 2,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,16</t>
+          <t>0,19; 1,79</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,83</t>
+          <t>0,83; 1,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,66; 1,26</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3542</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9697</t>
+          <t>0; 9620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9872</t>
+          <t>0; 8385</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11547</t>
+          <t>0; 12536</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1325; 7585</t>
+          <t>1372; 7829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1301; 7698</t>
+          <t>1417; 8365</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5492</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9591</t>
+          <t>914; 8259</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>527; 6139</t>
+          <t>674; 5846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1378; 11779</t>
+          <t>2243; 11255</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8947</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7581</t>
+          <t>0; 7671</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3489; 11507</t>
+          <t>3286; 11135</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5167; 15972</t>
+          <t>5018; 15473</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5696</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3576</t>
+          <t>0; 5663</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1860; 7724</t>
+          <t>2225; 8858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2536; 9280</t>
+          <t>2577; 10009</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2335</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2810</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>562; 5154</t>
+          <t>559; 5286</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>576; 6230</t>
+          <t>597; 5650</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3735; 17563</t>
+          <t>3935; 17198</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13469; 29134</t>
+          <t>14057; 29193</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19316; 39603</t>
+          <t>21586; 40987</t>
         </is>
       </c>
     </row>
